--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N31_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N31_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.79522799067137</v>
+        <v>9.554224548484099</v>
       </c>
       <c r="D2" t="n">
-        <v>25.16445906432324</v>
+        <v>4.089224597952526</v>
       </c>
       <c r="E2" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F2" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.82114134724156</v>
+        <v>4.358435468926754</v>
       </c>
       <c r="D3" t="n">
-        <v>26.4016541846917</v>
+        <v>4.290268805012402</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F3" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.35214547219361</v>
+        <v>4.282223639231463</v>
       </c>
       <c r="D4" t="n">
-        <v>15.83260909108165</v>
+        <v>2.572798977300768</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F4" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.39669103971289</v>
+        <v>9.976962293953346</v>
       </c>
       <c r="D5" t="n">
-        <v>59.21422451187158</v>
+        <v>9.622311483179132</v>
       </c>
       <c r="E5" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F5" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.28404413537673</v>
+        <v>4.433657171998719</v>
       </c>
       <c r="D6" t="n">
-        <v>19.58990136074603</v>
+        <v>3.18335897112123</v>
       </c>
       <c r="E6" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F6" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.67017593875369</v>
+        <v>9.696403590047474</v>
       </c>
       <c r="D7" t="n">
-        <v>57.9917733060314</v>
+        <v>9.423663162230104</v>
       </c>
       <c r="E7" t="n">
-        <v>16.58726121642359</v>
+        <v>2.695429947668834</v>
       </c>
       <c r="F7" t="n">
-        <v>17.72410161882206</v>
+        <v>2.880166513058585</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
